--- a/client posts status.xlsx
+++ b/client posts status.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nandagopal\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\client posting\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F92BB43-FE5E-448B-9E2A-65E62424D6FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69F50CBC-A35D-42A0-98E2-D15609E0F9A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{FF3F5B0C-C890-4C84-898F-5F723B2BFDE4}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="23">
   <si>
     <t xml:space="preserve">content title </t>
   </si>
@@ -102,6 +102,9 @@
   </si>
   <si>
     <t xml:space="preserve">food express </t>
+  </si>
+  <si>
+    <t>test</t>
   </si>
 </sst>
 </file>
@@ -728,7 +731,9 @@
       <c r="G9" s="1"/>
     </row>
     <row r="10" spans="1:14" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="1"/>
+      <c r="A10" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>

--- a/client posts status.xlsx
+++ b/client posts status.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\client posting\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69F50CBC-A35D-42A0-98E2-D15609E0F9A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F429BB76-A34F-4E40-AB1E-06324B56E120}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{FF3F5B0C-C890-4C84-898F-5F723B2BFDE4}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="24">
   <si>
     <t xml:space="preserve">content title </t>
   </si>
@@ -105,6 +105,9 @@
   </si>
   <si>
     <t>test</t>
+  </si>
+  <si>
+    <t>test 2</t>
   </si>
 </sst>
 </file>
@@ -742,7 +745,9 @@
       <c r="G10" s="1"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="1"/>
+      <c r="A11" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>

--- a/client posts status.xlsx
+++ b/client posts status.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\client posting\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F429BB76-A34F-4E40-AB1E-06324B56E120}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42DCA573-2AC3-49A0-B15B-52FE3737638C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{FF3F5B0C-C890-4C84-898F-5F723B2BFDE4}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="29">
   <si>
     <t xml:space="preserve">content title </t>
   </si>
@@ -104,10 +104,25 @@
     <t xml:space="preserve">food express </t>
   </si>
   <si>
-    <t>test</t>
-  </si>
-  <si>
-    <t>test 2</t>
+    <t>jameela clinic</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>portico</t>
+  </si>
+  <si>
+    <t>yet to post - need to change the password of social media</t>
+  </si>
+  <si>
+    <t>reel and poster</t>
+  </si>
+  <si>
+    <t>not received the poster</t>
+  </si>
+  <si>
+    <t>pending - received content today</t>
   </si>
 </sst>
 </file>
@@ -169,7 +184,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -192,6 +207,9 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -532,7 +550,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8A56996-FF66-4C5C-B8E9-ED27BB02754A}">
-  <dimension ref="A1:N22"/>
+  <dimension ref="A1:N24"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="28.21875" customWidth="1"/>
@@ -541,6 +559,7 @@
     <col min="4" max="4" width="26.33203125" customWidth="1"/>
     <col min="5" max="5" width="21.5546875" customWidth="1"/>
     <col min="6" max="6" width="19.33203125" customWidth="1"/>
+    <col min="7" max="7" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" s="4" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.3">
@@ -562,7 +581,9 @@
       <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="8"/>
+      <c r="G1" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="H1" s="8"/>
       <c r="I1" s="8"/>
       <c r="J1" s="8"/>
@@ -695,12 +716,12 @@
       </c>
       <c r="G7" s="1"/>
     </row>
-    <row r="8" spans="1:14" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" ht="60.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>17</v>
@@ -708,101 +729,168 @@
       <c r="D8" s="2">
         <v>46076</v>
       </c>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1" t="s">
-        <v>18</v>
+      <c r="E8" s="2"/>
+      <c r="F8" s="9" t="s">
+        <v>28</v>
       </c>
       <c r="G8" s="1"/>
     </row>
-    <row r="9" spans="1:14" ht="36.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D9" s="2">
-        <v>46105</v>
+        <v>46076</v>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G9" s="1"/>
-    </row>
-    <row r="10" spans="1:14" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G9" s="9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="49.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="2">
+        <v>46105</v>
+      </c>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
+      <c r="B11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" s="2">
+        <v>46107</v>
+      </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
+      <c r="G11" s="1"/>
+    </row>
+    <row r="12" spans="1:14" ht="43.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="2">
+        <v>46080</v>
+      </c>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
+    <row r="13" spans="1:14" ht="43.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13" s="2">
+        <v>46080</v>
+      </c>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
+    <row r="14" spans="1:14" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D14" s="2">
+        <v>46081</v>
+      </c>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
+    <row r="15" spans="1:14" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" s="2">
+        <v>46082</v>
+      </c>
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
+    <row r="16" spans="1:14" ht="49.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" s="2">
+        <v>46083</v>
+      </c>
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
+    <row r="17" spans="1:6" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D17" s="2">
+        <v>46083</v>
+      </c>
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -842,6 +930,22 @@
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
     </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" s="1"/>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" s="1"/>
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/client posts status.xlsx
+++ b/client posts status.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\client posting\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42DCA573-2AC3-49A0-B15B-52FE3737638C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5184C3C-8C84-4CDF-8170-F71075100E7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{FF3F5B0C-C890-4C84-898F-5F723B2BFDE4}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="29">
   <si>
     <t xml:space="preserve">content title </t>
   </si>
@@ -122,7 +122,7 @@
     <t>not received the poster</t>
   </si>
   <si>
-    <t>pending - received content today</t>
+    <t>reel received 25-02-2026</t>
   </si>
 </sst>
 </file>
@@ -729,9 +729,11 @@
       <c r="D8" s="2">
         <v>46076</v>
       </c>
-      <c r="E8" s="2"/>
+      <c r="E8" s="2">
+        <v>46078</v>
+      </c>
       <c r="F8" s="9" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="G8" s="1"/>
     </row>
@@ -792,7 +794,9 @@
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
+      <c r="G11" s="9" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="12" spans="1:14" ht="43.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">

--- a/client posts status.xlsx
+++ b/client posts status.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\client posting\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5184C3C-8C84-4CDF-8170-F71075100E7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC683A9D-73E5-4EDE-BFEF-013800EB429C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{FF3F5B0C-C890-4C84-898F-5F723B2BFDE4}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="28">
   <si>
     <t xml:space="preserve">content title </t>
   </si>
@@ -117,9 +117,6 @@
   </si>
   <si>
     <t>reel and poster</t>
-  </si>
-  <si>
-    <t>not received the poster</t>
   </si>
   <si>
     <t>reel received 25-02-2026</t>
@@ -771,13 +768,13 @@
       <c r="D10" s="2">
         <v>46105</v>
       </c>
-      <c r="E10" s="1"/>
+      <c r="E10" s="2">
+        <v>46078</v>
+      </c>
       <c r="F10" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>27</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="G10" s="1"/>
     </row>
     <row r="11" spans="1:14" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
@@ -795,7 +792,7 @@
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
       <c r="G11" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="43.8" customHeight="1" x14ac:dyDescent="0.3">

--- a/client posts status.xlsx
+++ b/client posts status.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\client posting\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC683A9D-73E5-4EDE-BFEF-013800EB429C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{139D3AC2-5C5F-47F5-AA26-B6C469132E9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{FF3F5B0C-C890-4C84-898F-5F723B2BFDE4}"/>
   </bookViews>
@@ -113,13 +113,13 @@
     <t>portico</t>
   </si>
   <si>
-    <t>yet to post - need to change the password of social media</t>
-  </si>
-  <si>
     <t>reel and poster</t>
   </si>
   <si>
-    <t>reel received 25-02-2026</t>
+    <t xml:space="preserve">reel received (chest pain) </t>
+  </si>
+  <si>
+    <t>reel received - yet to post - need to change the password of social media</t>
   </si>
 </sst>
 </file>
@@ -556,7 +556,7 @@
     <col min="4" max="4" width="26.33203125" customWidth="1"/>
     <col min="5" max="5" width="21.5546875" customWidth="1"/>
     <col min="6" max="6" width="19.33203125" customWidth="1"/>
-    <col min="7" max="7" width="20.6640625" customWidth="1"/>
+    <col min="7" max="7" width="23.6640625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" s="4" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.3">
@@ -608,7 +608,6 @@
       <c r="F2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="1"/>
     </row>
     <row r="3" spans="1:14" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -629,7 +628,6 @@
       <c r="F3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="1"/>
     </row>
     <row r="4" spans="1:14" s="7" customFormat="1" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
@@ -671,7 +669,6 @@
       <c r="F5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G5" s="1"/>
     </row>
     <row r="6" spans="1:14" ht="60.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
@@ -690,7 +687,6 @@
       <c r="F6" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G6" s="1"/>
     </row>
     <row r="7" spans="1:14" ht="60.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
@@ -711,7 +707,6 @@
       <c r="F7" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G7" s="1"/>
     </row>
     <row r="8" spans="1:14" ht="60.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
@@ -732,7 +727,6 @@
       <c r="F8" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="G8" s="1"/>
     </row>
     <row r="9" spans="1:14" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
@@ -752,7 +746,7 @@
         <v>18</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="49.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -774,7 +768,6 @@
       <c r="F10" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G10" s="1"/>
     </row>
     <row r="11" spans="1:14" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
@@ -791,9 +784,7 @@
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
-      <c r="G11" s="9" t="s">
-        <v>27</v>
-      </c>
+      <c r="G11" s="9"/>
     </row>
     <row r="12" spans="1:14" ht="43.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
@@ -810,13 +801,16 @@
       </c>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
+      <c r="G12" s="9" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="13" spans="1:14" ht="43.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>17</v>
